--- a/output/pdf_financials_xlsx/CULT.xlsx
+++ b/output/pdf_financials_xlsx/CULT.xlsx
@@ -1910,13 +1910,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>3.524905</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>4.372412</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>4.22742</v>
       </c>
     </row>
     <row r="93">
@@ -3179,7 +3179,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -3470,7 +3474,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E27" s="5" t="n">
         <v>3.524905</v>
       </c>

--- a/output/pdf_financials_xlsx/CULT.xlsx
+++ b/output/pdf_financials_xlsx/CULT.xlsx
@@ -581,13 +581,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>1.20639</v>
+        <v>1.975052</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1.833931</v>
+        <v>2.803926</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.813602</v>
+        <v>1.390079</v>
       </c>
     </row>
     <row r="11">
@@ -602,10 +602,10 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-1.833777</v>
+        <v>-2.803772</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.808383</v>
+        <v>-1.38486</v>
       </c>
     </row>
     <row r="12">
@@ -974,13 +974,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.00017</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.134033</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.010038</v>
       </c>
     </row>
     <row r="35">
@@ -1006,13 +1006,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.00017</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.134033</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.010038</v>
       </c>
     </row>
     <row r="37">
@@ -1198,13 +1198,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.048615</v>
+        <v>0.048445</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.187201</v>
+        <v>0.053168</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.025833</v>
+        <v>0.015795</v>
       </c>
     </row>
     <row r="49">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E99" s="5" t="n">
@@ -5752,7 +5752,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E101" s="5" t="n">
